--- a/satisfaction_surveys/027_patient_satisfaction_questionnaire--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/027_patient_satisfaction_questionnaire--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_intro</t>
+          <t>patient_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Patient Satisfaction Questionnaire</t>
+          <t>1. Form Intro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>2. Patient Contact Info</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How likely are you to recommend this healthcare provider?</t>
+          <t>3. How likely are you to recommend this healthcare provider?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How satisfied are you with the care you received?</t>
+          <t>4. How satisfied are you with the care you received?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How likely are you to use this healthcare provider again?</t>
+          <t>5. How likely are you to use this healthcare provider again?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What was the primary reason for your visit?</t>
+          <t>6. What was the primary reason for your visit?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How would you rate the communication with your healthcare provider?</t>
+          <t>7. How would you rate the communication with your healthcare provider?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What time of day do you prefer for your appointment schedule?</t>
+          <t>8. What time of day do you prefer for your appointment schedule?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How would you rate the waiting time prior to your visit?</t>
+          <t>9. How would you rate the waiting time prior to your visit?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Would you like to be contacted by the healthcare provider for any reason?</t>
+          <t>10. Would you like to be contacted by the healthcare provider for any reason?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Is there anything else you would like to add?</t>
+          <t>11. Is there anything else you would like to add?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>12. How likely are you to recommend this healthcare service to others?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How likely are you to recommend this healthcare provider to a friend or family member?</t>
+          <t>13. How would you rate the overall experience?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>question_13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>14. Thank you for taking the time to share your feedback!</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,251 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_13</t>
+          <t>question_14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How likely are you to return to this healthcare provider?</t>
+          <t>15. Additional comments</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question_14</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional comments</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_summary</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Form Summary</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_15</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How likely are you to recommend this healthcare service to others?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_16</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Additional comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How would you rate the overall experience?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Additional comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_end</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Form End</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Is there anything else you would like to add?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Additional comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Thank you for taking the time to share your feedback!</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,493 +896,493 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'patient_contact_info'}</t>
+          <t>patient_contact_info</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Patient Contact Info'}</t>
+          <t>Patient Contact Info</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'family_member_contact_info'}</t>
+          <t>family_member_contact_info</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Family Member Contact Info'}</t>
+          <t>Family Member Contact Info</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'healthcare_provider_contact_info'}</t>
+          <t>healthcare_provider_contact_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Healthcare Provider Contact Info'}</t>
+          <t>Healthcare Provider Contact Info</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_likely'}</t>
+          <t>not_very_likely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not Very Likely'}</t>
+          <t>Not Very Likely</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All Likely'}</t>
+          <t>Not at All Likely</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_likely'}</t>
+          <t>not_very_likely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not Very Likely'}</t>
+          <t>Not Very Likely</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All Likely'}</t>
+          <t>Not at All Likely</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_15_minutes'}</t>
+          <t>less_than_15_minutes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 15 minutes'}</t>
+          <t>Less than 15 minutes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'16-30_minutes'}</t>
+          <t>16-30_minutes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': '16-30 minutes'}</t>
+          <t>16-30 minutes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'31-60_minutes'}</t>
+          <t>31-60_minutes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': '31-60 minutes'}</t>
+          <t>31-60 minutes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_1_hour'}</t>
+          <t>more_than_1_hour</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'More than 1 hour'}</t>
+          <t>More than 1 hour</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1394,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1411,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1428,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_likely'}</t>
+          <t>not_very_likely</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Not Very Likely'}</t>
+          <t>Not Very Likely</t>
         </is>
       </c>
     </row>
@@ -1675,216 +1445,80 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All Likely'}</t>
+          <t>Not at All Likely</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_likely'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Not Very Likely'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_likely'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All Likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>question_15_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'label':_'very_likely'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'label': 'Very Likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>question_15_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'label':_'somewhat_likely'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'label': 'Somewhat Likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>question_15_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'label':_'not_very_likely'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'label': 'Not Very Likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>question_15_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'label':_'not_at_all_likely'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'label': 'Not at All Likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'label':_'excellent'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'label': 'Excellent'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'label':_'good'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'label': 'Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'label':_'fair'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'label': 'Fair'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'label':_'poor'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
